--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_168_R17.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_168_R17.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.1074</v>
+        <v>10.014</v>
       </c>
       <c r="E2" t="n">
-        <v>7.548</v>
+        <v>7.6227</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5593</v>
+        <v>2.3913</v>
       </c>
       <c r="G2" t="n">
         <v>7.0158</v>
@@ -610,13 +610,13 @@
         <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1971</v>
+        <v>1.1037</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0949</v>
+        <v>0.1696</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1022</v>
+        <v>0.9342</v>
       </c>
       <c r="V2" t="n">
         <v>2.8223</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.0024</v>
+        <v>9.484299999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>9.6471</v>
+        <v>10.8266</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6447</v>
+        <v>-1.3423</v>
       </c>
       <c r="G3" t="n">
         <v>4.2642</v>
@@ -688,13 +688,13 @@
         <v>3.0154</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.8701</v>
+        <v>-0.3881</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3205</v>
+        <v>-0.141</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5496</v>
+        <v>-0.2471</v>
       </c>
       <c r="V3" t="n">
         <v>3.7527</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. KEITA</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5091</v>
+        <v>1.9729</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9729</v>
+        <v>1.3692</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4639</v>
+        <v>0.6037</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4461</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4861</v>
+        <v>-0.3396</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0401</v>
+        <v>0.4217</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6185</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9193</v>
+        <v>-0.5679</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6993</v>
+        <v>1.2146</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1725</v>
+        <v>-0.5646</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4331</v>
+        <v>0.2283</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.7929</v>
       </c>
       <c r="P4" t="n">
         <v>-0.232</v>
@@ -766,19 +766,19 @@
         <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1532</v>
+        <v>1.0506</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3724</v>
+        <v>0.8101</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2192</v>
+        <v>0.2405</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>S. KEITA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7302</v>
+        <v>1.7677</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2945</v>
+        <v>2.2652</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4357</v>
+        <v>-0.4975</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08210000000000001</v>
+        <v>1.4461</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3396</v>
+        <v>1.4861</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4217</v>
+        <v>-0.0401</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6467000000000001</v>
+        <v>2.6185</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5679</v>
+        <v>1.9193</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2146</v>
+        <v>0.6993</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5646</v>
+        <v>-1.1725</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2283</v>
+        <v>-0.4331</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7929</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P5" t="n">
         <v>-0.232</v>
@@ -844,19 +844,19 @@
         <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8079</v>
+        <v>0.4118</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.6647</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0725</v>
+        <v>-0.2528</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3234</v>
+        <v>-0.2561</v>
       </c>
       <c r="E6" t="n">
         <v>0.0214</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3448</v>
+        <v>-0.2776</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3014</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.022</v>
+        <v>0.0452</v>
       </c>
       <c r="T6" t="n">
         <v>-0.0668</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0448</v>
+        <v>0.112</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7186</v>
+        <v>-0.9038</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4003</v>
+        <v>0.2823</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1188</v>
+        <v>-1.186</v>
       </c>
       <c r="G7" t="n">
         <v>-0.7226</v>
@@ -1000,13 +1000,13 @@
         <v>3.2473</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3444</v>
+        <v>0.1592</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1775</v>
+        <v>0.0595</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1669</v>
+        <v>0.0997</v>
       </c>
       <c r="V7" t="n">
         <v>-2.428</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9339</v>
+        <v>-1.2377</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8387</v>
+        <v>-0.224</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7726</v>
+        <v>-1.0137</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3381</v>
+        <v>-0.0535</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9566</v>
+        <v>0.1573</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3815</v>
+        <v>-0.2108</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4386</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08400000000000001</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3546</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7767</v>
+        <v>-0.0535</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0406</v>
+        <v>0.1573</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7361</v>
+        <v>-0.2108</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1</v>
+        <v>-0.112</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4876</v>
+        <v>-0.224</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.112</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>-1.0722</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>N. LAPROVITTOLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2439</v>
+        <v>-1.2947</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9024</v>
+        <v>1.499</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3416</v>
+        <v>-2.7938</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.5517</v>
+        <v>-1.0344</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.7551</v>
+        <v>0.1836</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7967</v>
+        <v>-1.218</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8423</v>
+        <v>0.7058</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.1</v>
+        <v>-0.077</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2576</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.7094</v>
+        <v>-1.7401</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6551</v>
+        <v>0.2606</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.0543</v>
+        <v>-2.0008</v>
       </c>
       <c r="P9" t="n">
         <v>1.6237</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7834</v>
+        <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6531</v>
+        <v>-0.8118</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4604</v>
+        <v>-0.279</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1927</v>
+        <v>-0.5329</v>
       </c>
       <c r="V9" t="n">
-        <v>0.031</v>
+        <v>-1.0722</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6393</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.6083</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3049</v>
+        <v>-1.5327</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.224</v>
+        <v>0.4416</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0809</v>
+        <v>-1.9743</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0535</v>
+        <v>-1.3381</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1573</v>
+        <v>-0.9566</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2108</v>
+        <v>-0.3815</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.4386</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.3546</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0535</v>
+        <v>-1.7767</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1573</v>
+        <v>-1.0406</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2108</v>
+        <v>-0.7361</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1792</v>
+        <v>0.5012</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.224</v>
+        <v>0.0905</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0448</v>
+        <v>0.4107</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X10" t="n">
         <v>-1.0722</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N. LAPROVITTOLA</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7323</v>
+        <v>-2.0272</v>
       </c>
       <c r="E11" t="n">
-        <v>1.2631</v>
+        <v>-1.1816</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9954</v>
+        <v>-0.8457</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0344</v>
+        <v>-4.5517</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1836</v>
+        <v>-2.7551</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.218</v>
+        <v>-1.7967</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7058</v>
+        <v>-1.8423</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.077</v>
+        <v>-2.1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.2576</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7401</v>
+        <v>-2.7094</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2606</v>
+        <v>-0.6551</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.0008</v>
+        <v>-2.0543</v>
       </c>
       <c r="P11" t="n">
         <v>1.6237</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6237</v>
+        <v>2.7834</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2494</v>
+        <v>0.8698</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5149</v>
+        <v>0.1812</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7345</v>
+        <v>0.6886</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0722</v>
+        <v>0.031</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0722</v>
+        <v>1.6393</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1444</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2842</v>
+        <v>-2.1491</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3448</v>
+        <v>0.5807</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6291</v>
+        <v>-2.7299</v>
       </c>
       <c r="G12" t="n">
         <v>-3.3743</v>
@@ -1390,13 +1390,13 @@
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0901</v>
+        <v>0.2251</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4323</v>
+        <v>-0.1964</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5223</v>
+        <v>0.4215</v>
       </c>
       <c r="V12" t="n">
         <v>0.5361</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.8279</v>
+        <v>-5.4844</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.3675</v>
+        <v>-5.2928</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4604</v>
+        <v>-0.1916</v>
       </c>
       <c r="G13" t="n">
         <v>-6.7373</v>
@@ -1468,13 +1468,13 @@
         <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.253</v>
+        <v>0.0905</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1766</v>
+        <v>-0.1019</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0764</v>
+        <v>0.1924</v>
       </c>
       <c r="V13" t="n">
         <v>0.9304</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.980000000000002</v>
+        <v>8.353200000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>17.8369</v>
+        <v>18.2103</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.857199999999999</v>
+        <v>-9.857399999999998</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.3051</v>
+        <v>-5.305100000000002</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2155999999999998</v>
+        <v>0.2155999999999989</v>
       </c>
       <c r="I14" t="n">
         <v>-5.520799999999999</v>
@@ -1531,7 +1531,7 @@
         <v>-20.5169</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.494899999999999</v>
+        <v>-5.4949</v>
       </c>
       <c r="O14" t="n">
         <v>-15.0224</v>
@@ -1546,16 +1546,16 @@
         <v>18.5562</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7721</v>
+        <v>3.1452</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5931</v>
+        <v>0.9665000000000002</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1789</v>
+        <v>2.1788</v>
       </c>
       <c r="V14" t="n">
-        <v>4.714099999999998</v>
+        <v>4.714099999999999</v>
       </c>
       <c r="W14" t="n">
         <v>14.7893</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8632</v>
+        <v>4.7053</v>
       </c>
       <c r="E15" t="n">
-        <v>9.51</v>
+        <v>9.745900000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.6469</v>
+        <v>-5.0406</v>
       </c>
       <c r="G15" t="n">
         <v>8.3329</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3822</v>
+        <v>0.4599</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0351</v>
+        <v>0.2008</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.347</v>
+        <v>0.2592</v>
       </c>
       <c r="V15" t="n">
         <v>-1.0722</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8538</v>
+        <v>3.5507</v>
       </c>
       <c r="E16" t="n">
-        <v>7.0934</v>
+        <v>6.3857</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.2396</v>
+        <v>-2.835</v>
       </c>
       <c r="G16" t="n">
         <v>1.7905</v>
@@ -1702,13 +1702,13 @@
         <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1149</v>
+        <v>0.8118</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1993</v>
+        <v>0.4916</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0843</v>
+        <v>0.3203</v>
       </c>
       <c r="V16" t="n">
         <v>0.2525</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6652</v>
+        <v>2.2499</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4893</v>
+        <v>3.0175</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-0.7675999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>0.6449</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6286</v>
+        <v>0.2133</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3031</v>
+        <v>-0.1687</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3255</v>
+        <v>0.382</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7983</v>
+        <v>1.2669</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1507</v>
+        <v>0.2686</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6476</v>
+        <v>0.9983</v>
       </c>
       <c r="G18" t="n">
         <v>1.3918</v>
@@ -1858,13 +1858,13 @@
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.2515</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4086</v>
+        <v>-0.2906</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1914</v>
+        <v>0.5421</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0722</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2441</v>
+        <v>0.0533</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8665</v>
+        <v>1.3947</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6224</v>
+        <v>-1.3415</v>
       </c>
       <c r="G19" t="n">
         <v>0.2741</v>
@@ -1936,13 +1936,13 @@
         <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2921</v>
+        <v>0.1013</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3778</v>
+        <v>-0.094</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0857</v>
+        <v>0.1953</v>
       </c>
       <c r="V19" t="n">
         <v>0.1418</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0514</v>
+        <v>0.0387</v>
       </c>
       <c r="E20" t="n">
         <v>1.0638</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1152</v>
+        <v>-1.0252</v>
       </c>
       <c r="G20" t="n">
         <v>-0.38</v>
@@ -2014,13 +2014,13 @@
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1353</v>
+        <v>-0.0452</v>
       </c>
       <c r="T20" t="n">
         <v>-0.224</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0887</v>
+        <v>0.1788</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4635</v>
+        <v>-1.3019</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09320000000000001</v>
+        <v>-0.4965</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5568</v>
+        <v>-0.8053</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9224</v>
@@ -2092,13 +2092,13 @@
         <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5311</v>
+        <v>0.6928</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1246</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5935</v>
+        <v>0.1579</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3329</v>
+        <v>-2.2137</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5993</v>
+        <v>-0.6827</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2663</v>
+        <v>-1.5311</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8005</v>
+        <v>-0.6943</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2556</v>
+        <v>-0.4598</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4551</v>
+        <v>-0.2345</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.4687</v>
+        <v>0.4287</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.5055</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0368</v>
+        <v>0.3476</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6681</v>
+        <v>-1.123</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2499</v>
+        <v>-0.5409</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4183</v>
+        <v>-0.5821</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4639</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5324</v>
+        <v>-0.736</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9709</v>
+        <v>-0.8487</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4384</v>
+        <v>0.1127</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.2166</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5361</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7071</v>
+        <v>-2.3431</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6263</v>
+        <v>-3.3634</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0809</v>
+        <v>1.0203</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6943</v>
+        <v>-0.8005</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4598</v>
+        <v>-1.2556</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2345</v>
+        <v>0.4551</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4287</v>
+        <v>-1.4687</v>
       </c>
       <c r="K23" t="n">
-        <v>0.08119999999999999</v>
+        <v>-1.5055</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3476</v>
+        <v>0.0368</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.123</v>
+        <v>0.6681</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5409</v>
+        <v>0.2499</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5821</v>
+        <v>0.4183</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.8556</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.2294</v>
+        <v>-0.5425</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.7924</v>
+        <v>-0.735</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4371</v>
+        <v>0.1924</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W23" t="n">
-        <v>3.2166</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1444</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.8588</v>
+        <v>-4.6248</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.7287</v>
+        <v>-5.2569</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1301</v>
+        <v>0.6321</v>
       </c>
       <c r="G24" t="n">
         <v>-1.4486</v>
@@ -2326,13 +2326,13 @@
         <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.3406</v>
+        <v>-1.1066</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.643</v>
+        <v>-1.1712</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6976</v>
+        <v>0.0646</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6778999999999999</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.9906</v>
+        <v>-6.2157</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.4556</v>
+        <v>-2.2197</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.535</v>
+        <v>-3.996</v>
       </c>
       <c r="G25" t="n">
         <v>-2.8833</v>
@@ -2404,13 +2404,13 @@
         <v>1.6237</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5017</v>
+        <v>0.2732</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1098</v>
+        <v>0.1261</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3918</v>
+        <v>0.1472</v>
       </c>
       <c r="V25" t="n">
         <v>-1.7501</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.979699999999999</v>
+        <v>-4.8344</v>
       </c>
       <c r="E26" t="n">
-        <v>9.856999999999999</v>
+        <v>9.857000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-17.8371</v>
+        <v>-14.6916</v>
       </c>
       <c r="G26" t="n">
-        <v>5.305099999999998</v>
+        <v>5.305099999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2156999999999996</v>
+        <v>-0.2157000000000004</v>
       </c>
       <c r="I26" t="n">
         <v>5.5209</v>
@@ -2458,7 +2458,7 @@
         <v>20.517</v>
       </c>
       <c r="K26" t="n">
-        <v>5.494899999999999</v>
+        <v>5.4949</v>
       </c>
       <c r="L26" t="n">
         <v>15.0221</v>
@@ -2482,13 +2482,13 @@
         <v>12.7576</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.7721</v>
+        <v>0.3734999999999998</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.179</v>
+        <v>-2.1789</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5929999999999999</v>
+        <v>2.5525</v>
       </c>
       <c r="V26" t="n">
         <v>-4.7142</v>
